--- a/Excel/MinionTable.xlsx
+++ b/Excel/MinionTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MillenniumOfCultivation\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2AF6B3-EB98-4451-903C-5C6D7F579F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C8A490-DB98-4BF7-B758-0EA9E9150C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Stat</t>
+    <t>적</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -98,7 +98,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -106,8 +107,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -144,41 +144,48 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -459,193 +466,178 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.4140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.08203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="11.08203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.4140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.08203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.58203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="7">
+        <v>10000001</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="6">
-        <v>10000001</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6">
-        <v>10000001</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="6">
-        <v>10000001</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6">
-        <v>10000001</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="6">
-        <v>10000001</v>
-      </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="6">
-        <v>10000001</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="6">
-        <v>10000001</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="6">
-        <v>10000001</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="6">
-        <v>10000001</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" s="6">
-        <v>10000001</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7">
+        <v>10000002</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="7">
+        <v>10000003</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7">
+        <v>10000004</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="7">
+        <v>10000005</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="7">
+        <v>10000006</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="7">
+        <v>10000007</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="7">
+        <v>10000008</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="7">
+        <v>10000009</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="7">
+        <v>10000010</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
